--- a/inst/shiny-examples/MassIBItools/Extras/tables/Instruction_Tables.xlsx
+++ b/inst/shiny-examples/MassIBItools/Extras/tables/Instruction_Tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben.Block\OneDrive - Tetra Tech, Inc\GitHub\MassIBItools\inst\shiny-examples\MassIBItools\Extras\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben.Block\OneDrive - Tetra Tech, Inc\GitHub\IDEMtools\inst\shiny-examples\MassIBItools\Extras\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="185" documentId="6_{FCDEF830-16B4-406E-A93E-DA0A90D83908}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{A0B6C60F-C8E0-4F65-AA9B-2552FDC7CD19}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2460" windowWidth="19440" windowHeight="15000" activeTab="5" xr2:uid="{3B3719AA-49C9-406B-B2F9-D3A39525E496}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{3B3719AA-49C9-406B-B2F9-D3A39525E496}"/>
   </bookViews>
   <sheets>
     <sheet name="Instr_table1" sheetId="3" r:id="rId1"/>
@@ -2003,9 +2003,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2232,27 +2235,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD18DA69-7EC7-4262-B3E6-9A14BFB313F1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0E0F61B-E5F7-4E18-B122-367D9E9A27FA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ee0f1bd9-88a9-4065-9041-4ab71245ad05"/>
-    <ds:schemaRef ds:uri="f184d54a-0942-4fe6-a117-6eb5ddd114d9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2277,9 +2268,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0E0F61B-E5F7-4E18-B122-367D9E9A27FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD18DA69-7EC7-4262-B3E6-9A14BFB313F1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="ee0f1bd9-88a9-4065-9041-4ab71245ad05"/>
+    <ds:schemaRef ds:uri="f184d54a-0942-4fe6-a117-6eb5ddd114d9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/inst/shiny-examples/MassIBItools/Extras/tables/Instruction_Tables.xlsx
+++ b/inst/shiny-examples/MassIBItools/Extras/tables/Instruction_Tables.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben.Block\OneDrive - Tetra Tech, Inc\GitHub\IDEMtools\inst\shiny-examples\MassIBItools\Extras\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="619" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{F1EE1E42-1777-411F-8FAC-74FF41A52714}"/>
+  <xr:revisionPtr revIDLastSave="637" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{824E8E62-F8B0-4386-A047-6A047912DB89}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2460" windowWidth="19440" windowHeight="15000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2460" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bug_N" sheetId="1" r:id="rId1"/>
-    <sheet name="Bug_NC" sheetId="2" r:id="rId2"/>
-    <sheet name="Bug_SW" sheetId="3" r:id="rId3"/>
-    <sheet name="Bug_SE" sheetId="4" r:id="rId4"/>
-    <sheet name="Fish_WS" sheetId="5" r:id="rId5"/>
-    <sheet name="Fish_WL" sheetId="6" r:id="rId6"/>
-    <sheet name="Fish_BL" sheetId="7" r:id="rId7"/>
-    <sheet name="Fish_BH" sheetId="8" r:id="rId8"/>
+    <sheet name="Instr_Table" sheetId="9" r:id="rId1"/>
+    <sheet name="Bug_N" sheetId="1" r:id="rId2"/>
+    <sheet name="Bug_NC" sheetId="2" r:id="rId3"/>
+    <sheet name="Bug_SW" sheetId="3" r:id="rId4"/>
+    <sheet name="Bug_SE" sheetId="4" r:id="rId5"/>
+    <sheet name="Fish_WS" sheetId="5" r:id="rId6"/>
+    <sheet name="Fish_WL" sheetId="6" r:id="rId7"/>
+    <sheet name="Fish_BL" sheetId="7" r:id="rId8"/>
+    <sheet name="Fish_BH" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="163">
   <si>
     <t>Metric (abbrev)</t>
   </si>
@@ -364,13 +365,178 @@
   </si>
   <si>
     <t>DA&lt;1: 100* MetVal / 9.75 OR DA&gt;1:100* MetVal/(9.71 * logDA +  9.75)</t>
+  </si>
+  <si>
+    <t>Column Name</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Domain (allowable entries)</t>
+  </si>
+  <si>
+    <t>Null Allowed</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>INDEX_NAME</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>INDEX_REGION</t>
+  </si>
+  <si>
+    <t>Must match one of the five allowable entries (which tells the R code which IBI to apply to each sample).</t>
+  </si>
+  <si>
+    <t>STATIONID</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>SAMPLEID</t>
+  </si>
+  <si>
+    <t>Unique sample identifier (typically comprised of the site name, sample date, and replicate number).</t>
+  </si>
+  <si>
+    <t>LAT</t>
+  </si>
+  <si>
+    <t>numeric</t>
+  </si>
+  <si>
+    <t>real number, in decimal degrees</t>
+  </si>
+  <si>
+    <t>NAD83 datum</t>
+  </si>
+  <si>
+    <t>LONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAD83 datum. Longitude values in North America (west of the prime meridian) should be negative . </t>
+  </si>
+  <si>
+    <t>COLLDATE</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Date on which the sample was collected.</t>
+  </si>
+  <si>
+    <t>COLLMETH</t>
+  </si>
+  <si>
+    <t>TAXAID</t>
+  </si>
+  <si>
+    <t>N_TAXA</t>
+  </si>
+  <si>
+    <t>non-negative real number</t>
+  </si>
+  <si>
+    <t>Number of individuals.</t>
+  </si>
+  <si>
+    <t>EXCLUDE</t>
+  </si>
+  <si>
+    <t>TRUE, FALSE</t>
+  </si>
+  <si>
+    <t>NONTARGET</t>
+  </si>
+  <si>
+    <t>PHYLUM</t>
+  </si>
+  <si>
+    <t>CLASS</t>
+  </si>
+  <si>
+    <t>ORDER</t>
+  </si>
+  <si>
+    <t>FAMILY</t>
+  </si>
+  <si>
+    <t>SUBFAMILY</t>
+  </si>
+  <si>
+    <t>TRIBE</t>
+  </si>
+  <si>
+    <t>GENUS</t>
+  </si>
+  <si>
+    <t>FFG</t>
+  </si>
+  <si>
+    <t>CG, CF, PR, SC, SH (select one)</t>
+  </si>
+  <si>
+    <t>TOLVAL</t>
+  </si>
+  <si>
+    <t>number ranging from 0-10</t>
+  </si>
+  <si>
+    <t>LIFE_CYCLE</t>
+  </si>
+  <si>
+    <t>uni, semi, multi (select one)</t>
+  </si>
+  <si>
+    <t>IDEM_2017_Bugs or IDEM_2017_Fish</t>
+  </si>
+  <si>
+    <t>Only two allowable entries (IDEM_2017_Bugs or IDEM_2017_Fish).</t>
+  </si>
+  <si>
+    <t>Bugs_N, Bugs_NC, Bugs_SW, Bugs_SE, Fish_WS, Fish_WL, Fish_BL, Fish_BH</t>
+  </si>
+  <si>
+    <t>Taxonomic identification of organisms in each sample. See [TaxaTranslator table](https://github.com/Blocktt/IDEMtools/tree/main/Data_Prep).</t>
+  </si>
+  <si>
+    <t>Redundant (non-distinct) taxa should marked "TRUE". Criteria for designating redundant taxa should be consistent with the [ExcludeDecisionCriteria document](https://github.com/Blocktt/IDEMtools/tree/main/Data_Prep).</t>
+  </si>
+  <si>
+    <t>Non-target taxa should be marked "TRUE". Designations should match with those in the [Taxa Attribute tables](https://github.com/Blocktt/IDEMtools/tree/main/Data_Prep).</t>
+  </si>
+  <si>
+    <t>Several IBI metrics are based on Order (e.g., % EPT taxa). Entries should be consistent with the phylogeny in the [Taxa Attribute tables](https://github.com/Blocktt/IDEMtools/tree/main/Data_Prep).</t>
+  </si>
+  <si>
+    <t>Entries should be consistent with the phylogeny in the [Taxa Attribute tables](https://github.com/Blocktt/IDEMtools/tree/main/Data_Prep).</t>
+  </si>
+  <si>
+    <t>Primary Functional Feeding Group. Choose from, can have multiple entries separated by comma: collector-gatherer (CG), collector-filterer (CF), predator (PR), scraper (SC), or shredder (SH). FFG trait assignments should match with those in the [Taxa Attribute tables](https://github.com/Blocktt/IDEMtools/tree/main/Data_Prep).</t>
+  </si>
+  <si>
+    <t>Taxa with tolerance values ranging from 0 to 3 are considered 'intolerant' to anthropogenic disturbance and are included in the 'intolerant' metric calculations. Those with values ranging from 7 to 10 are included in the 'tolerant' metrics.</t>
+  </si>
+  <si>
+    <t>Number of broods or generations of an organism in a year (also referred to as 'voltinism'): univoltine (UNI), semivoltine (SEMI), or multivoltine (MULTI).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,8 +552,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,6 +591,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -425,7 +610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -439,6 +624,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,6 +925,369 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A600CB5-0FBB-4C6F-ACC1-0B9BA1C4A60F}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="98.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="29.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -810,7 +1379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1D1177-BF58-4690-B0F3-E4B8B9C44B80}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -924,7 +1493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71BD45DD-C9A0-4868-ABC6-135358DC1150}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1026,7 +1595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AE666A-6F6C-4CC2-A2DC-6E828F6056A7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1130,7 +1699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588ADA60-339A-4CB8-94EA-E826EAEBFF0A}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1267,7 +1836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00690039-BC6A-4645-958A-044B1BAF5C2A}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1381,7 +1950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AA0657-29F5-4616-9040-346197EC86A3}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1506,7 +2075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78449ECD-F460-41A5-AB1D-5EAA5A7C52BF}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
